--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -530,7 +530,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -558,7 +558,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -573,7 +573,7 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
+    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die Durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>
@@ -657,13 +657,13 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
   </si>
   <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -720,7 +720,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>Patient, für den die Durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -748,7 +748,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The encounter or episode of care that establishes the context for this event.</t>
@@ -767,7 +767,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -849,7 +849,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -875,7 +875,7 @@
   </si>
   <si>
     <t>Refrenz auf Practitioner, PractitionerRole, Organization, 
-der/die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+der/die die Durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
 auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -911,9 +911,9 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
-Planeintrag (MedicationRequest). Es muss nicht zwingend eine geplante Abgabe referenziert werden, da es auch durchgeführte 
-Abgaben ohne geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
+    <t>Referenz auf zugehörige Geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
+Planeintrag (MedicationRequest). Es muss nicht zwingend eine Geplante Abgabe referenziert werden, da es auch durchgeführte 
+Abgaben ohne Geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -530,7 +530,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Verpflichtende Angabe des 'e-Med Groupidentifiers' der Geplanten Abgabe, sofern diese existiert.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -3060,7 +3060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
@@ -3076,10 +3076,10 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
